--- a/src/test/resources/TestDriver/Hearst_GHK/ActivityData/GHK_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_GHK/ActivityData/GHK_AP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\fyntrac-data\src\test\resources\TestDriver\Hearst_GHK\ActivityData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E605946C-E926-4B70-AE59-4E37D097F822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17820E19-74AF-4583-A392-CAE4D915CCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Accounting_Policy" sheetId="8" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Accounting_Policy!$A$1:$D$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Accounting_Policy!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="62">
   <si>
     <t>product_code</t>
   </si>
@@ -210,13 +210,25 @@
   </si>
   <si>
     <t>GHK_PRTDIG_US_New_1999_Print</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>parent_child</t>
+  </si>
+  <si>
+    <t>parent_code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -230,6 +242,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -249,15 +268,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{D8617A8A-47C3-4D32-B703-EAC4C017702E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -470,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1194FE4C-FBC1-4D63-8FD6-C5A14E8D6200}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63.85546875" customWidth="1"/>
@@ -479,7 +500,7 @@
     <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,8 +513,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -506,8 +533,14 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -520,8 +553,14 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -534,8 +573,11 @@
       <c r="D4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -548,8 +590,11 @@
       <c r="D5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -562,8 +607,14 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -576,8 +627,14 @@
       <c r="D7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -590,8 +647,11 @@
       <c r="D8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -604,8 +664,11 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -618,8 +681,14 @@
       <c r="D10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -632,8 +701,14 @@
       <c r="D11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -646,8 +721,14 @@
       <c r="D12" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -660,8 +741,14 @@
       <c r="D13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -674,8 +761,11 @@
       <c r="D14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -688,8 +778,14 @@
       <c r="D15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -702,8 +798,14 @@
       <c r="D16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -716,8 +818,11 @@
       <c r="D17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -730,8 +835,14 @@
       <c r="D18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -744,8 +855,14 @@
       <c r="D19" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -758,8 +875,11 @@
       <c r="D20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -772,8 +892,11 @@
       <c r="D21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -786,8 +909,11 @@
       <c r="D22" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -800,8 +926,11 @@
       <c r="D23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -814,8 +943,11 @@
       <c r="D24" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -828,8 +960,14 @@
       <c r="D25" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -842,8 +980,14 @@
       <c r="D26" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -856,8 +1000,14 @@
       <c r="D27" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -870,8 +1020,14 @@
       <c r="D28" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -884,8 +1040,14 @@
       <c r="D29" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -898,8 +1060,14 @@
       <c r="D30" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -912,8 +1080,14 @@
       <c r="D31" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -926,8 +1100,11 @@
       <c r="D32" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -940,8 +1117,14 @@
       <c r="D33" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -954,8 +1137,11 @@
       <c r="D34" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -968,8 +1154,14 @@
       <c r="D35" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -982,8 +1174,14 @@
       <c r="D36" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -996,8 +1194,11 @@
       <c r="D37" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -1010,8 +1211,11 @@
       <c r="D38" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -1024,8 +1228,11 @@
       <c r="D39" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -1038,8 +1245,14 @@
       <c r="D40" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -1052,8 +1265,14 @@
       <c r="D41" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -1066,8 +1285,11 @@
       <c r="D42" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -1080,8 +1302,14 @@
       <c r="D43" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -1094,8 +1322,14 @@
       <c r="D44" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -1108,8 +1342,14 @@
       <c r="D45" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -1122,8 +1362,11 @@
       <c r="D46" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -1136,8 +1379,14 @@
       <c r="D47" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -1150,8 +1399,11 @@
       <c r="D48" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1164,8 +1416,14 @@
       <c r="D49" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1177,6 +1435,12 @@
       </c>
       <c r="D50" t="s">
         <v>5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
